--- a/Files/Testdata/login_credentials.xlsx
+++ b/Files/Testdata/login_credentials.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13460" windowHeight="7860" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13460" windowHeight="7860" firstSheet="2" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Admin" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,14 @@
     <sheet name="OSAM" sheetId="7" r:id="rId9"/>
     <sheet name="BASICS" sheetId="8" r:id="rId10"/>
     <sheet name="AMPS" sheetId="9" r:id="rId11"/>
+    <sheet name="Class_Beta" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
   <si>
     <t>Username</t>
   </si>
@@ -125,6 +126,12 @@
   </si>
   <si>
     <t>JulzJoshJerdz25#</t>
+  </si>
+  <si>
+    <t>chance_terry</t>
+  </si>
+  <si>
+    <t>]&gt;byz11C1O!g</t>
   </si>
 </sst>
 </file>
@@ -562,6 +569,39 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B27"/>
